--- a/data/trans_camb/P62-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P62-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-14,07; 0,92</t>
+          <t>-13,8; 1,09</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-20,05; -4,42</t>
+          <t>-18,32; -4,12</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,76; 11,38</t>
+          <t>-5,1; 12,42</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,2; 13,07</t>
+          <t>2,46; 13,17</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,35; 11,45</t>
+          <t>0,74; 12,29</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,6; 21,98</t>
+          <t>11,98; 21,66</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 9,09</t>
+          <t>-0,43; 8,74</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,46; 5,44</t>
+          <t>-3,67; 5,91</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8,74; 17,56</t>
+          <t>8,7; 17,86</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-23,62; 2,18</t>
+          <t>-23,36; 2,03</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-32,08; -8,23</t>
+          <t>-30,64; -7,73</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-9,71; 21,55</t>
+          <t>-8,69; 23,1</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8,1; 60,43</t>
+          <t>8,78; 60,47</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,29; 53,48</t>
+          <t>1,92; 55,96</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>46,21; 103,65</t>
+          <t>44,52; 105,65</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 27,32</t>
+          <t>-1,16; 25,69</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-9,04; 16,32</t>
+          <t>-9,64; 18,18</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>22,56; 52,38</t>
+          <t>23,69; 54,12</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-22,12; -9,0</t>
+          <t>-21,59; -8,13</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-19,02; -5,88</t>
+          <t>-19,2; -5,8</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-12,23; 3,6</t>
+          <t>-11,96; 2,97</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,69; 10,39</t>
+          <t>1,21; 10,98</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,48; 9,65</t>
+          <t>0,49; 9,96</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,74; 15,95</t>
+          <t>7,27; 16,19</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-4,44; 3,51</t>
+          <t>-4,59; 3,34</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,89; 4,44</t>
+          <t>-3,77; 4,21</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,55; 10,94</t>
+          <t>2,27; 10,41</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-36,65; -17,1</t>
+          <t>-36,34; -16,2</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-31,43; -11,14</t>
+          <t>-31,97; -11,11</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-20,7; 6,94</t>
+          <t>-20,14; 5,63</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,96; 52,79</t>
+          <t>4,8; 55,51</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,65; 48,85</t>
+          <t>1,95; 51,64</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,7; 82,73</t>
+          <t>29,31; 85,06</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-12,4; 10,69</t>
+          <t>-12,74; 10,44</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-10,64; 13,89</t>
+          <t>-10,33; 12,94</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,89; 33,21</t>
+          <t>6,48; 31,94</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-26,1; -11,13</t>
+          <t>-26,38; -10,73</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-19,31; -3,27</t>
+          <t>-19,18; -3,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-8,48; 10,06</t>
+          <t>-9,03; 9,79</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,12; 6,12</t>
+          <t>-4,76; 6,57</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,4; 7,36</t>
+          <t>-3,93; 7,28</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,12; 56,24</t>
+          <t>8,34; 58,07</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-10,4; -0,64</t>
+          <t>-9,94; -0,76</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-6,45; 3,4</t>
+          <t>-6,43; 2,69</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,08; 40,2</t>
+          <t>7,25; 41,97</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-42,98; -20,59</t>
+          <t>-42,56; -20,2</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-30,67; -6,24</t>
+          <t>-30,97; -5,9</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-13,95; 18,92</t>
+          <t>-14,26; 18,53</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-17,69; 25,96</t>
+          <t>-16,87; 28,6</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-15,74; 32,25</t>
+          <t>-14,22; 31,21</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>30,29; 258,25</t>
+          <t>31,24; 244,28</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-25,9; -1,83</t>
+          <t>-24,98; -2,31</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-16,27; 9,8</t>
+          <t>-16,17; 7,63</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>18,37; 114,68</t>
+          <t>19,54; 119,6</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-9,02; 5,08</t>
+          <t>-8,85; 5,07</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,95; 7,34</t>
+          <t>-6,16; 7,24</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-7,51; 6,79</t>
+          <t>-7,36; 6,5</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 7,78</t>
+          <t>-1,93; 8,14</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,29; 13,8</t>
+          <t>3,43; 13,64</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,76; 16,33</t>
+          <t>7,52; 17,11</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 5,91</t>
+          <t>-2,14; 5,84</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,12; 10,57</t>
+          <t>2,97; 10,96</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,7; 12,12</t>
+          <t>4,02; 12,22</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-16,73; 11,67</t>
+          <t>-16,56; 11,03</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-11,21; 16,12</t>
+          <t>-11,57; 15,44</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-14,33; 14,81</t>
+          <t>-14,12; 14,26</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-5,92; 32,01</t>
+          <t>-6,38; 33,44</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>10,76; 56,56</t>
+          <t>11,84; 55,46</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>22,81; 66,74</t>
+          <t>24,68; 68,14</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-5,88; 17,69</t>
+          <t>-5,87; 17,34</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>5,66; 31,48</t>
+          <t>7,84; 33,27</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>9,89; 36,32</t>
+          <t>10,77; 36,56</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-14,1; -6,94</t>
+          <t>-13,86; -6,97</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-11,59; -4,86</t>
+          <t>-11,88; -4,67</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-4,57; 3,51</t>
+          <t>-4,89; 3,51</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,83; 6,89</t>
+          <t>1,76; 6,79</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,81; 8,16</t>
+          <t>2,92; 8,33</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11,97; 36,22</t>
+          <t>11,92; 35,15</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 2,3</t>
+          <t>-2,16; 2,1</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 4,1</t>
+          <t>-0,45; 3,74</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>8,14; 23,3</t>
+          <t>8,18; 21,92</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-25,03; -13,3</t>
+          <t>-24,7; -13,3</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-20,64; -9,42</t>
+          <t>-21,02; -8,86</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-8,0; 6,66</t>
+          <t>-8,49; 6,65</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>7,01; 29,37</t>
+          <t>6,64; 29,12</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>10,56; 34,94</t>
+          <t>10,92; 35,62</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>47,7; 142,68</t>
+          <t>46,95; 147,57</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-5,61; 6,69</t>
+          <t>-5,9; 6,14</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 11,75</t>
+          <t>-1,24; 10,83</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>22,51; 65,35</t>
+          <t>22,54; 60,62</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P62-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P62-Habitat-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3,71</t>
+          <t>5,17</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,14</t>
+          <t>16,36</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>13,27</t>
+          <t>13,34</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-13,8; 1,09</t>
+          <t>-14,07; 0,81</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-18,32; -4,12</t>
+          <t>-19,12; -3,86</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,1; 12,42</t>
+          <t>-3,27; 13,67</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,46; 13,17</t>
+          <t>2,02; 13,07</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,74; 12,29</t>
+          <t>0,62; 11,25</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,98; 21,66</t>
+          <t>11,23; 21,71</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 8,74</t>
+          <t>-0,6; 8,73</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 5,91</t>
+          <t>-3,85; 5,24</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8,7; 17,86</t>
+          <t>8,55; 17,83</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>71,75%</t>
+          <t>68,49%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>37,23%</t>
+          <t>37,43%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-23,36; 2,03</t>
+          <t>-23,83; 1,61</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-30,64; -7,73</t>
+          <t>-31,53; -7,19</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-8,69; 23,1</t>
+          <t>-5,41; 26,75</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8,78; 60,47</t>
+          <t>8,25; 63,45</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,92; 55,96</t>
+          <t>2,04; 53,52</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>44,52; 105,65</t>
+          <t>41,57; 103,18</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 25,69</t>
+          <t>-1,76; 26,48</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-9,64; 18,18</t>
+          <t>-9,99; 15,73</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>23,69; 54,12</t>
+          <t>22,53; 53,8</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-4,39</t>
+          <t>-3,45</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>11,64</t>
+          <t>11,36</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>6,64</t>
+          <t>6,73</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-21,59; -8,13</t>
+          <t>-21,24; -8,06</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-19,2; -5,8</t>
+          <t>-18,5; -5,75</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-11,96; 2,97</t>
+          <t>-10,57; 4,97</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,21; 10,98</t>
+          <t>1,14; 10,29</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,49; 9,96</t>
+          <t>-0,04; 9,6</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,27; 16,19</t>
+          <t>7,02; 16,55</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-4,59; 3,34</t>
+          <t>-4,53; 3,39</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 4,21</t>
+          <t>-4,04; 3,73</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,27; 10,41</t>
+          <t>2,6; 10,55</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-7,81%</t>
+          <t>-6,14%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>53,15%</t>
+          <t>51,88%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>19,58%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-36,34; -16,2</t>
+          <t>-35,97; -15,84</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-31,97; -11,11</t>
+          <t>-31,38; -11,33</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-20,14; 5,63</t>
+          <t>-17,56; 9,43</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,8; 55,51</t>
+          <t>4,96; 53,25</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,95; 51,64</t>
+          <t>-0,25; 49,14</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,31; 85,06</t>
+          <t>28,31; 87,49</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-12,74; 10,44</t>
+          <t>-12,55; 10,28</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-10,33; 12,94</t>
+          <t>-10,99; 11,33</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,48; 31,94</t>
+          <t>7,52; 32,59</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,67</t>
+          <t>2,17</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>31,77</t>
+          <t>9,1</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>20,37</t>
+          <t>8,54</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-26,38; -10,73</t>
+          <t>-26,7; -11,39</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-19,18; -3,0</t>
+          <t>-18,84; -3,03</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-9,03; 9,79</t>
+          <t>-6,75; 11,07</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,76; 6,57</t>
+          <t>-4,76; 6,88</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,93; 7,28</t>
+          <t>-4,07; 7,36</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,34; 58,07</t>
+          <t>4,07; 14,89</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-9,94; -0,76</t>
+          <t>-10,54; -1,18</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-6,43; 2,69</t>
+          <t>-6,23; 3,07</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,25; 41,97</t>
+          <t>3,79; 13,41</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>122,61%</t>
+          <t>35,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>54,27%</t>
+          <t>22,74%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-42,56; -20,2</t>
+          <t>-42,89; -21,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-30,97; -5,9</t>
+          <t>-30,39; -5,41</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-14,26; 18,53</t>
+          <t>-10,73; 20,97</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-16,87; 28,6</t>
+          <t>-16,77; 30,6</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-14,22; 31,21</t>
+          <t>-14,69; 32,33</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>31,24; 244,28</t>
+          <t>13,55; 65,32</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-24,98; -2,31</t>
+          <t>-26,12; -3,2</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-16,17; 7,63</t>
+          <t>-15,67; 8,61</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>19,54; 119,6</t>
+          <t>9,69; 38,2</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-0,31</t>
+          <t>-0,16</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,03</t>
+          <t>11,9</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>8,0</t>
+          <t>7,86</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-8,85; 5,07</t>
+          <t>-8,49; 4,57</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-6,16; 7,24</t>
+          <t>-5,7; 7,47</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-7,36; 6,5</t>
+          <t>-7,41; 7,38</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 8,14</t>
+          <t>-2,15; 7,81</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,43; 13,64</t>
+          <t>3,0; 13,46</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,52; 17,11</t>
+          <t>6,76; 16,4</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 5,84</t>
+          <t>-2,2; 6,13</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,97; 10,96</t>
+          <t>2,51; 10,54</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4,02; 12,22</t>
+          <t>3,7; 11,85</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-0,64%</t>
+          <t>-0,31%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>44,08%</t>
+          <t>43,59%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,12%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-16,56; 11,03</t>
+          <t>-16,28; 9,94</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-11,57; 15,44</t>
+          <t>-10,96; 16,8</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-14,12; 14,26</t>
+          <t>-13,97; 16,27</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-6,38; 33,44</t>
+          <t>-7,09; 31,87</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>11,84; 55,46</t>
+          <t>9,64; 55,24</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>24,68; 68,14</t>
+          <t>22,63; 67,34</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-5,87; 17,34</t>
+          <t>-5,85; 18,09</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>7,84; 33,27</t>
+          <t>6,62; 31,22</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>10,77; 36,56</t>
+          <t>10,3; 35,65</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-0,43</t>
+          <t>0,58</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>18,66</t>
+          <t>12,21</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>12,07</t>
+          <t>8,9</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-13,86; -6,97</t>
+          <t>-13,98; -7,08</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-11,88; -4,67</t>
+          <t>-11,52; -4,76</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-4,89; 3,51</t>
+          <t>-3,29; 4,53</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,76; 6,79</t>
+          <t>1,65; 6,94</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,92; 8,33</t>
+          <t>2,85; 8,19</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11,92; 35,15</t>
+          <t>9,73; 14,76</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 2,1</t>
+          <t>-2,15; 2,12</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 3,74</t>
+          <t>-0,38; 3,74</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>8,18; 21,92</t>
+          <t>6,78; 11,0</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-0,78%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>75,72%</t>
+          <t>49,58%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>33,88%</t>
+          <t>24,99%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-24,7; -13,3</t>
+          <t>-24,68; -13,44</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-21,02; -8,86</t>
+          <t>-20,6; -9,21</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-8,49; 6,65</t>
+          <t>-5,85; 8,69</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>6,64; 29,12</t>
+          <t>6,35; 29,67</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>10,92; 35,62</t>
+          <t>11,08; 35,38</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>46,95; 147,57</t>
+          <t>37,59; 64,33</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-5,9; 6,14</t>
+          <t>-5,88; 6,18</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 10,83</t>
+          <t>-1,03; 10,69</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>22,54; 60,62</t>
+          <t>18,14; 31,7</t>
         </is>
       </c>
     </row>
